--- a/LoanOfficer-A/2023/54 Induleikha.xlsx
+++ b/LoanOfficer-A/2023/54 Induleikha.xlsx
@@ -813,7 +813,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -822,7 +822,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>3600</v>
+        <v>5000</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -855,7 +855,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>8400</v>
+        <v>7000</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1023,9 +1023,15 @@
       <c r="A8" s="1">
         <v>6</v>
       </c>
-      <c r="B8" s="3"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="1"/>
+      <c r="B8" s="3">
+        <v>45572</v>
+      </c>
+      <c r="C8" s="4">
+        <v>700</v>
+      </c>
+      <c r="D8" s="1">
+        <v>1</v>
+      </c>
       <c r="E8" s="1">
         <v>36</v>
       </c>
@@ -1049,9 +1055,15 @@
       <c r="A9" s="1">
         <v>7</v>
       </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="1"/>
+      <c r="B9" s="3">
+        <v>45573</v>
+      </c>
+      <c r="C9" s="4">
+        <v>700</v>
+      </c>
+      <c r="D9" s="1">
+        <v>1</v>
+      </c>
       <c r="E9" s="1">
         <v>37</v>
       </c>

--- a/LoanOfficer-A/2023/54 Induleikha.xlsx
+++ b/LoanOfficer-A/2023/54 Induleikha.xlsx
@@ -813,7 +813,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -822,7 +822,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>5000</v>
+        <v>7100</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -855,7 +855,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>7000</v>
+        <v>4900</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1087,9 +1087,15 @@
       <c r="A10" s="1">
         <v>8</v>
       </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="1"/>
+      <c r="B10" s="3">
+        <v>45586</v>
+      </c>
+      <c r="C10" s="4">
+        <v>700</v>
+      </c>
+      <c r="D10" s="1">
+        <v>1</v>
+      </c>
       <c r="E10" s="1">
         <v>38</v>
       </c>
@@ -1113,9 +1119,15 @@
       <c r="A11" s="1">
         <v>9</v>
       </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="1"/>
+      <c r="B11" s="3">
+        <v>45593</v>
+      </c>
+      <c r="C11" s="4">
+        <v>700</v>
+      </c>
+      <c r="D11" s="1">
+        <v>1</v>
+      </c>
       <c r="E11" s="1">
         <v>39</v>
       </c>
@@ -1139,9 +1151,15 @@
       <c r="A12" s="1">
         <v>10</v>
       </c>
-      <c r="B12" s="3"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="1"/>
+      <c r="B12" s="3">
+        <v>45600</v>
+      </c>
+      <c r="C12" s="4">
+        <v>700</v>
+      </c>
+      <c r="D12" s="1">
+        <v>1</v>
+      </c>
       <c r="E12" s="1">
         <v>40</v>
       </c>

--- a/LoanOfficer-A/2023/54 Induleikha.xlsx
+++ b/LoanOfficer-A/2023/54 Induleikha.xlsx
@@ -813,7 +813,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -822,7 +822,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>7100</v>
+        <v>8500</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -855,7 +855,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>4900</v>
+        <v>3500</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1183,9 +1183,15 @@
       <c r="A13" s="1">
         <v>11</v>
       </c>
-      <c r="B13" s="3"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="1"/>
+      <c r="B13" s="3">
+        <v>45607</v>
+      </c>
+      <c r="C13" s="4">
+        <v>700</v>
+      </c>
+      <c r="D13" s="1">
+        <v>1</v>
+      </c>
       <c r="E13" s="1">
         <v>41</v>
       </c>
@@ -1209,9 +1215,15 @@
       <c r="A14" s="1">
         <v>12</v>
       </c>
-      <c r="B14" s="3"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="1"/>
+      <c r="B14" s="3">
+        <v>45618</v>
+      </c>
+      <c r="C14" s="4">
+        <v>700</v>
+      </c>
+      <c r="D14" s="1">
+        <v>1</v>
+      </c>
       <c r="E14" s="1">
         <v>42</v>
       </c>

--- a/LoanOfficer-A/2023/54 Induleikha.xlsx
+++ b/LoanOfficer-A/2023/54 Induleikha.xlsx
@@ -606,7 +606,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -813,7 +813,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -822,7 +822,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>8500</v>
+        <v>9200</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -855,7 +855,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>3500</v>
+        <v>2800</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1247,9 +1247,15 @@
       <c r="A15" s="1">
         <v>13</v>
       </c>
-      <c r="B15" s="3"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="1"/>
+      <c r="B15" s="3">
+        <v>45625</v>
+      </c>
+      <c r="C15" s="4">
+        <v>700</v>
+      </c>
+      <c r="D15" s="1">
+        <v>1</v>
+      </c>
       <c r="E15" s="1">
         <v>43</v>
       </c>

--- a/LoanOfficer-A/2023/54 Induleikha.xlsx
+++ b/LoanOfficer-A/2023/54 Induleikha.xlsx
@@ -606,7 +606,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -813,7 +813,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -822,7 +822,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>9200</v>
+        <v>9900</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -855,7 +855,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>2800</v>
+        <v>2100</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1279,9 +1279,15 @@
       <c r="A16" s="1">
         <v>14</v>
       </c>
-      <c r="B16" s="3"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="1"/>
+      <c r="B16" s="3">
+        <v>45599</v>
+      </c>
+      <c r="C16" s="4">
+        <v>700</v>
+      </c>
+      <c r="D16" s="1">
+        <v>1</v>
+      </c>
       <c r="E16" s="1">
         <v>44</v>
       </c>

--- a/LoanOfficer-A/2023/54 Induleikha.xlsx
+++ b/LoanOfficer-A/2023/54 Induleikha.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <t xml:space="preserve">Loan Amount: </t>
   </si>
@@ -102,6 +102,9 @@
   </si>
   <si>
     <t>Paid (weeks):</t>
+  </si>
+  <si>
+    <t>date of completion</t>
   </si>
 </sst>
 </file>
@@ -217,7 +220,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -278,6 +281,9 @@
     </xf>
     <xf numFmtId="15" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -606,7 +612,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -624,8 +630,8 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B2" s="21"/>
-      <c r="C2" s="21"/>
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B5" s="13"/>
@@ -705,20 +711,20 @@
       <c r="C16" s="14"/>
     </row>
     <row r="17" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B17" s="22" t="s">
+      <c r="B17" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="C17" s="22"/>
+      <c r="C17" s="23"/>
     </row>
     <row r="19" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B19" s="17"/>
       <c r="C19" s="17"/>
     </row>
     <row r="21" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B21" s="22" t="s">
+      <c r="B21" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="C21" s="22"/>
+      <c r="C21" s="23"/>
     </row>
     <row r="22" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B22" s="14"/>
@@ -813,7 +819,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -822,7 +828,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>9900</v>
+        <v>12000</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -837,8 +843,13 @@
       </c>
       <c r="D2" s="6"/>
       <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="7"/>
+      <c r="F2" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="G2" s="21">
+        <f>B3+G1*7</f>
+        <v>45650</v>
+      </c>
       <c r="H2" s="6"/>
       <c r="I2" s="6"/>
       <c r="J2" s="7" t="s">
@@ -846,7 +857,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -855,7 +866,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>2100</v>
+        <v>0</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1280,7 +1291,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="3">
-        <v>45599</v>
+        <v>45629</v>
       </c>
       <c r="C16" s="4">
         <v>700</v>
@@ -1311,9 +1322,15 @@
       <c r="A17" s="1">
         <v>15</v>
       </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="1"/>
+      <c r="B17" s="3">
+        <v>45635</v>
+      </c>
+      <c r="C17" s="4">
+        <v>700</v>
+      </c>
+      <c r="D17" s="1">
+        <v>1</v>
+      </c>
       <c r="E17" s="1">
         <v>45</v>
       </c>
@@ -1337,9 +1354,15 @@
       <c r="A18" s="1">
         <v>16</v>
       </c>
-      <c r="B18" s="3"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="1"/>
+      <c r="B18" s="3">
+        <v>45643</v>
+      </c>
+      <c r="C18" s="4">
+        <v>700</v>
+      </c>
+      <c r="D18" s="1">
+        <v>1</v>
+      </c>
       <c r="E18" s="1">
         <v>46</v>
       </c>
@@ -1363,9 +1386,15 @@
       <c r="A19" s="1">
         <v>17</v>
       </c>
-      <c r="B19" s="3"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="1"/>
+      <c r="B19" s="3">
+        <v>45649</v>
+      </c>
+      <c r="C19" s="4">
+        <v>700</v>
+      </c>
+      <c r="D19" s="1">
+        <v>1</v>
+      </c>
       <c r="E19" s="1">
         <v>47</v>
       </c>
